--- a/Excel/OccupationConfig.xlsx
+++ b/Excel/OccupationConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C33FB1-D564-4D68-8FFA-ED5065E3B291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626FC27C-8DAC-41D6-B7CB-FE5CBDECEB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
   <si>
     <t>Id</t>
   </si>
@@ -305,6 +305,26 @@
   </si>
   <si>
     <t>40001000,40002000,40003000</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warrior</t>
+  </si>
+  <si>
+    <t>Mage</t>
+  </si>
+  <si>
+    <t>Hunter</t>
+  </si>
+  <si>
+    <t>Summoner</t>
+  </si>
+  <si>
+    <t>OccupationName_EN</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1566,7 +1586,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1612,6 +1632,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="314">
     <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -2255,124 +2276,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:AH17"/>
+  <dimension ref="C1:AI17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="9.375" customWidth="1"/>
-    <col min="4" max="6" width="15.125" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
-    <col min="8" max="13" width="13.125" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="21" width="11.5" customWidth="1"/>
-    <col min="22" max="25" width="16.75" customWidth="1"/>
-    <col min="26" max="30" width="13.125" customWidth="1"/>
-    <col min="31" max="31" width="35.625" customWidth="1"/>
-    <col min="32" max="32" width="15.875" customWidth="1"/>
-    <col min="33" max="33" width="42.375" customWidth="1"/>
-    <col min="34" max="34" width="69.5" customWidth="1"/>
+    <col min="4" max="4" width="15.125" customWidth="1"/>
+    <col min="5" max="5" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="12.375" customWidth="1"/>
+    <col min="9" max="14" width="13.125" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="22" width="11.5" customWidth="1"/>
+    <col min="23" max="26" width="16.75" customWidth="1"/>
+    <col min="27" max="31" width="13.125" customWidth="1"/>
+    <col min="32" max="32" width="35.625" customWidth="1"/>
+    <col min="33" max="33" width="15.875" customWidth="1"/>
+    <col min="34" max="34" width="42.375" customWidth="1"/>
+    <col min="35" max="35" width="69.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:34" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="3:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="T3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="X3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="Y3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Z3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="AA3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AA3" s="5" t="s">
+      <c r="AB3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="AB3" s="5" t="s">
+      <c r="AC3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AC3" s="5" t="s">
+      <c r="AD3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AD3" s="5" t="s">
+      <c r="AE3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AE3" s="5" t="s">
+      <c r="AF3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AF3" s="5" t="s">
+      <c r="AG3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AH3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AI3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="3:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2380,111 +2410,114 @@
         <v>26</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="O4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="R4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="S4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="T4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="U4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="V4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="W4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="X4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="Y4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="AA4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AB4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AE4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AF4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AG4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="3" t="s">
+      <c r="AH4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AH4" s="3" t="s">
+      <c r="AI4" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="3:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>59</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>59</v>
@@ -2505,7 +2538,7 @@
         <v>59</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>60</v>
@@ -2526,7 +2559,7 @@
         <v>60</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V5" s="7" t="s">
         <v>59</v>
@@ -2553,22 +2586,25 @@
         <v>59</v>
       </c>
       <c r="AD5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE5" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="AE5" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="AF5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="AG5" s="3" t="s">
+      <c r="AG5" s="7" t="s">
         <v>61</v>
       </c>
       <c r="AH5" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="AI5" s="3" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="6" spans="3:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="8">
         <v>1</v>
       </c>
@@ -2576,40 +2612,40 @@
         <v>62</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F6" s="10">
+      <c r="G6" s="10">
         <v>1</v>
       </c>
-      <c r="G6" s="11">
+      <c r="H6" s="11">
         <v>5250</v>
       </c>
-      <c r="H6" s="11">
+      <c r="I6" s="11">
         <v>250</v>
       </c>
-      <c r="I6" s="11">
+      <c r="J6" s="11">
         <v>500</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="11">
         <v>75</v>
       </c>
-      <c r="K6" s="11">
+      <c r="L6" s="11">
         <v>160</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="11">
         <v>75</v>
       </c>
-      <c r="M6" s="11">
+      <c r="N6" s="11">
         <v>160</v>
       </c>
-      <c r="N6" s="11">
+      <c r="O6" s="11">
         <v>4.5</v>
       </c>
-      <c r="O6" s="11">
+      <c r="P6" s="11">
         <v>0.05</v>
-      </c>
-      <c r="P6" s="12">
-        <v>0</v>
       </c>
       <c r="Q6" s="12">
         <v>0</v>
@@ -2624,49 +2660,52 @@
         <v>0</v>
       </c>
       <c r="U6" s="12">
+        <v>0</v>
+      </c>
+      <c r="V6" s="12">
         <v>350</v>
-      </c>
-      <c r="V6" s="12">
-        <v>12</v>
       </c>
       <c r="W6" s="12">
         <v>12</v>
       </c>
-      <c r="X6" s="10">
-        <v>0</v>
+      <c r="X6" s="12">
+        <v>12</v>
       </c>
       <c r="Y6" s="10">
         <v>0</v>
       </c>
-      <c r="Z6" s="12">
-        <v>10</v>
+      <c r="Z6" s="10">
+        <v>0</v>
       </c>
       <c r="AA6" s="12">
         <v>10</v>
       </c>
       <c r="AB6" s="12">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AC6" s="12">
         <v>4</v>
       </c>
       <c r="AD6" s="12">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="12">
         <v>50000101</v>
       </c>
-      <c r="AE6" s="14" t="s">
+      <c r="AF6" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="AF6" s="14" t="s">
+      <c r="AG6" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="AG6" s="14" t="s">
+      <c r="AH6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="AH6" s="15" t="s">
+      <c r="AI6" s="15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="3:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="8">
         <v>2</v>
       </c>
@@ -2674,40 +2713,40 @@
         <v>68</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7" s="10">
         <v>1</v>
       </c>
-      <c r="G7" s="11">
+      <c r="H7" s="11">
         <v>3750</v>
       </c>
-      <c r="H7" s="11">
+      <c r="I7" s="11">
         <v>350</v>
       </c>
-      <c r="I7" s="11">
+      <c r="J7" s="11">
         <v>700</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="11">
         <v>75</v>
       </c>
-      <c r="K7" s="11">
+      <c r="L7" s="11">
         <v>120</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="11">
         <v>75</v>
       </c>
-      <c r="M7" s="11">
+      <c r="N7" s="11">
         <v>120</v>
       </c>
-      <c r="N7" s="11">
+      <c r="O7" s="11">
         <v>4.5</v>
       </c>
-      <c r="O7" s="11">
+      <c r="P7" s="11">
         <v>0.05</v>
-      </c>
-      <c r="P7" s="12">
-        <v>0</v>
       </c>
       <c r="Q7" s="12">
         <v>0</v>
@@ -2722,49 +2761,52 @@
         <v>0</v>
       </c>
       <c r="U7" s="12">
+        <v>0</v>
+      </c>
+      <c r="V7" s="12">
         <v>250</v>
-      </c>
-      <c r="V7" s="12">
-        <v>12</v>
       </c>
       <c r="W7" s="12">
         <v>12</v>
       </c>
-      <c r="X7" s="10">
-        <v>3</v>
+      <c r="X7" s="12">
+        <v>12</v>
       </c>
       <c r="Y7" s="10">
         <v>3</v>
       </c>
-      <c r="Z7" s="12">
-        <v>4</v>
+      <c r="Z7" s="10">
+        <v>3</v>
       </c>
       <c r="AA7" s="12">
         <v>4</v>
       </c>
       <c r="AB7" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC7" s="12">
         <v>6</v>
       </c>
       <c r="AD7" s="12">
+        <v>6</v>
+      </c>
+      <c r="AE7" s="12">
         <v>50000201</v>
       </c>
-      <c r="AE7" s="16" t="s">
+      <c r="AF7" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="AF7" s="14" t="s">
+      <c r="AG7" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="AG7" s="14" t="s">
+      <c r="AH7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="AH7" s="15" t="s">
+      <c r="AI7" s="15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="3:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="8">
         <v>3</v>
       </c>
@@ -2772,40 +2814,40 @@
         <v>73</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="10">
+      <c r="G8" s="10">
         <v>1</v>
       </c>
-      <c r="G8" s="11">
+      <c r="H8" s="11">
         <v>3750</v>
       </c>
-      <c r="H8" s="11">
+      <c r="I8" s="11">
         <v>350</v>
       </c>
-      <c r="I8" s="11">
+      <c r="J8" s="11">
         <v>700</v>
       </c>
-      <c r="J8" s="11">
+      <c r="K8" s="11">
         <v>75</v>
       </c>
-      <c r="K8" s="11">
+      <c r="L8" s="11">
         <v>120</v>
       </c>
-      <c r="L8" s="11">
+      <c r="M8" s="11">
         <v>75</v>
       </c>
-      <c r="M8" s="11">
+      <c r="N8" s="11">
         <v>120</v>
       </c>
-      <c r="N8" s="11">
+      <c r="O8" s="11">
         <v>4.5</v>
       </c>
-      <c r="O8" s="11">
+      <c r="P8" s="11">
         <v>0.05</v>
-      </c>
-      <c r="P8" s="12">
-        <v>0</v>
       </c>
       <c r="Q8" s="12">
         <v>0</v>
@@ -2820,49 +2862,52 @@
         <v>0</v>
       </c>
       <c r="U8" s="12">
+        <v>0</v>
+      </c>
+      <c r="V8" s="12">
         <v>250</v>
-      </c>
-      <c r="V8" s="12">
-        <v>12</v>
       </c>
       <c r="W8" s="12">
         <v>12</v>
       </c>
-      <c r="X8" s="10">
-        <v>3</v>
+      <c r="X8" s="12">
+        <v>12</v>
       </c>
       <c r="Y8" s="10">
         <v>3</v>
       </c>
-      <c r="Z8" s="12">
-        <v>4</v>
+      <c r="Z8" s="10">
+        <v>3</v>
       </c>
       <c r="AA8" s="12">
         <v>4</v>
       </c>
       <c r="AB8" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC8" s="12">
         <v>6</v>
       </c>
       <c r="AD8" s="12">
+        <v>6</v>
+      </c>
+      <c r="AE8" s="12">
         <v>50000301</v>
       </c>
-      <c r="AE8" s="16" t="s">
+      <c r="AF8" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="AF8" s="14" t="s">
+      <c r="AG8" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AG8" s="14" t="s">
+      <c r="AH8" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AH8" s="15" t="s">
+      <c r="AI8" s="15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="3:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="8">
         <v>4</v>
       </c>
@@ -2870,40 +2915,40 @@
         <v>78</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="10">
+      <c r="G9" s="10">
         <v>1</v>
       </c>
-      <c r="G9" s="11">
+      <c r="H9" s="11">
         <v>3750</v>
       </c>
-      <c r="H9" s="11">
+      <c r="I9" s="11">
         <v>350</v>
       </c>
-      <c r="I9" s="11">
+      <c r="J9" s="11">
         <v>700</v>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="11">
         <v>75</v>
       </c>
-      <c r="K9" s="11">
+      <c r="L9" s="11">
         <v>120</v>
       </c>
-      <c r="L9" s="11">
+      <c r="M9" s="11">
         <v>75</v>
       </c>
-      <c r="M9" s="11">
+      <c r="N9" s="11">
         <v>120</v>
       </c>
-      <c r="N9" s="11">
+      <c r="O9" s="11">
         <v>4.5</v>
       </c>
-      <c r="O9" s="11">
+      <c r="P9" s="11">
         <v>0.05</v>
-      </c>
-      <c r="P9" s="12">
-        <v>0</v>
       </c>
       <c r="Q9" s="12">
         <v>0</v>
@@ -2918,60 +2963,62 @@
         <v>0</v>
       </c>
       <c r="U9" s="12">
+        <v>0</v>
+      </c>
+      <c r="V9" s="12">
         <v>250</v>
-      </c>
-      <c r="V9" s="12">
-        <v>12</v>
       </c>
       <c r="W9" s="12">
         <v>12</v>
       </c>
-      <c r="X9" s="10">
-        <v>3</v>
+      <c r="X9" s="12">
+        <v>12</v>
       </c>
       <c r="Y9" s="10">
         <v>3</v>
       </c>
-      <c r="Z9" s="12">
-        <v>4</v>
+      <c r="Z9" s="10">
+        <v>3</v>
       </c>
       <c r="AA9" s="12">
         <v>4</v>
       </c>
       <c r="AB9" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC9" s="12">
         <v>6</v>
       </c>
       <c r="AD9" s="12">
+        <v>6</v>
+      </c>
+      <c r="AE9" s="12">
         <v>50000401</v>
       </c>
-      <c r="AE9" s="16" t="s">
+      <c r="AF9" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="AF9" s="14" t="s">
+      <c r="AG9" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AG9" s="14" t="s">
+      <c r="AH9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AH9" s="15" t="s">
+      <c r="AI9" s="15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="3:34" x14ac:dyDescent="0.2">
-      <c r="T11" s="13"/>
+    <row r="11" spans="3:35" x14ac:dyDescent="0.2">
       <c r="U11" s="13"/>
       <c r="V11" s="13"/>
       <c r="W11" s="13"/>
-      <c r="Z11" s="13"/>
+      <c r="X11" s="13"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="13"/>
       <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
     </row>
-    <row r="12" spans="3:34" x14ac:dyDescent="0.2">
-      <c r="T12" s="13"/>
+    <row r="12" spans="3:35" x14ac:dyDescent="0.2">
       <c r="U12" s="13"/>
       <c r="V12" s="13"/>
       <c r="W12" s="13"/>
@@ -2981,12 +3028,13 @@
       <c r="AA12" s="13"/>
       <c r="AB12" s="13"/>
       <c r="AC12" s="13"/>
+      <c r="AD12" s="13"/>
     </row>
-    <row r="16" spans="3:34" x14ac:dyDescent="0.2">
-      <c r="W16" s="13"/>
+    <row r="16" spans="3:35" x14ac:dyDescent="0.2">
+      <c r="X16" s="13"/>
     </row>
-    <row r="17" spans="23:23" x14ac:dyDescent="0.2">
-      <c r="W17" s="13"/>
+    <row r="17" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X17" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Excel/OccupationConfig.xlsx
+++ b/Excel/OccupationConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626FC27C-8DAC-41D6-B7CB-FE5CBDECEB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427D6B13-1BE0-4B71-A9F8-E59A11FB829D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationConfig" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>Id</t>
   </si>
@@ -308,9 +308,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Warrior</t>
-  </si>
-  <si>
     <t>Mage</t>
   </si>
   <si>
@@ -325,6 +322,22 @@
   </si>
   <si>
     <t>c</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warrior</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dark Warrior</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hero_5</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>混沌骑士</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -2298,7 +2311,7 @@
     <row r="1" spans="3:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E2" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2410,7 +2423,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>27</v>
@@ -2612,7 +2625,7 @@
         <v>62</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>63</v>
@@ -2713,7 +2726,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>69</v>
@@ -2814,7 +2827,7 @@
         <v>73</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>74</v>
@@ -2915,7 +2928,7 @@
         <v>78</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>79</v>
@@ -3005,6 +3018,107 @@
         <v>82</v>
       </c>
       <c r="AI9" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="3:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="8">
+        <v>5</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="11">
+        <v>3750</v>
+      </c>
+      <c r="I10" s="11">
+        <v>350</v>
+      </c>
+      <c r="J10" s="11">
+        <v>700</v>
+      </c>
+      <c r="K10" s="11">
+        <v>75</v>
+      </c>
+      <c r="L10" s="11">
+        <v>120</v>
+      </c>
+      <c r="M10" s="11">
+        <v>75</v>
+      </c>
+      <c r="N10" s="11">
+        <v>120</v>
+      </c>
+      <c r="O10" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>0</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
+      <c r="T10" s="12">
+        <v>0</v>
+      </c>
+      <c r="U10" s="12">
+        <v>0</v>
+      </c>
+      <c r="V10" s="12">
+        <v>350</v>
+      </c>
+      <c r="W10" s="12">
+        <v>12</v>
+      </c>
+      <c r="X10" s="12">
+        <v>12</v>
+      </c>
+      <c r="Y10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>10</v>
+      </c>
+      <c r="AB10" s="12">
+        <v>10</v>
+      </c>
+      <c r="AC10" s="12">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="12">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="12">
+        <v>50000401</v>
+      </c>
+      <c r="AF10" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG10" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH10" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI10" s="15" t="s">
         <v>67</v>
       </c>
     </row>

--- a/Excel/OccupationConfig.xlsx
+++ b/Excel/OccupationConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427D6B13-1BE0-4B71-A9F8-E59A11FB829D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA78411-C6CC-4264-86BE-430E8513330B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="94">
   <si>
     <t>Id</t>
   </si>
@@ -337,7 +337,15 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>混沌骑士</t>
+    <t>50001000,50002000,50003000</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>501,502,503</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨剑士</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -3026,7 +3034,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>89</v>
@@ -3107,16 +3115,16 @@
         <v>4</v>
       </c>
       <c r="AE10" s="12">
-        <v>50000401</v>
+        <v>50000501</v>
       </c>
       <c r="AF10" s="16" t="s">
         <v>80</v>
       </c>
       <c r="AG10" s="14" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH10" s="14" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI10" s="15" t="s">
         <v>67</v>

--- a/Excel/OccupationConfig.xlsx
+++ b/Excel/OccupationConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA78411-C6CC-4264-86BE-430E8513330B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE7E08B-6AD3-4D67-9176-52CF179BFB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationConfig" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="95">
   <si>
     <t>Id</t>
   </si>
@@ -346,6 +346,10 @@
   </si>
   <si>
     <t>巨剑士</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>55011102,55011201,55011301</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -3118,7 +3122,7 @@
         <v>50000501</v>
       </c>
       <c r="AF10" s="16" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AG10" s="14" t="s">
         <v>92</v>

--- a/Excel/OccupationConfig.xlsx
+++ b/Excel/OccupationConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE7E08B-6AD3-4D67-9176-52CF179BFB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5101EF1A-33D0-47B7-ACED-23BC9F2F436C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationConfig" sheetId="1" r:id="rId1"/>

--- a/Excel/OccupationConfig.xlsx
+++ b/Excel/OccupationConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5101EF1A-33D0-47B7-ACED-23BC9F2F436C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFC4EE3-CD29-4979-92DF-E44621B1C245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationConfig" sheetId="1" r:id="rId1"/>
@@ -3050,25 +3050,25 @@
         <v>1</v>
       </c>
       <c r="H10" s="11">
-        <v>3750</v>
+        <v>5250</v>
       </c>
       <c r="I10" s="11">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="J10" s="11">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="K10" s="11">
         <v>75</v>
       </c>
       <c r="L10" s="11">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="M10" s="11">
         <v>75</v>
       </c>
       <c r="N10" s="11">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="O10" s="11">
         <v>4.5</v>

--- a/Excel/OccupationConfig.xlsx
+++ b/Excel/OccupationConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFC4EE3-CD29-4979-92DF-E44621B1C245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5327D43F-D670-4819-933E-21A4343803D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -345,11 +345,11 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>巨剑士</t>
+    <t>55011102,55011201,55011301</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>55011102,55011201,55011301</t>
+    <t>巨刃士</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -3038,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>89</v>
@@ -3122,7 +3122,7 @@
         <v>50000501</v>
       </c>
       <c r="AF10" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG10" s="14" t="s">
         <v>92</v>
